--- a/data/__gene_data.xlsx
+++ b/data/__gene_data.xlsx
@@ -482,7 +482,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -527,14 +527,6 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <u val="single"/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -571,7 +563,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="23">
+  <cellStyleXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -595,9 +587,6 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -612,57 +601,56 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="22" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="22" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="9">
+  <cellStyles count="8">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Normal 2" xfId="21"/>
-    <cellStyle name="Normal 3" xfId="22"/>
-    <cellStyle name="*unknown*" xfId="20" builtinId="8"/>
+    <cellStyle name="Normal 2" xfId="20"/>
+    <cellStyle name="Normal 3" xfId="21"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -688,7 +676,7 @@
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0563C1"/>
+      <rgbColor rgb="FF0066CC"/>
       <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -904,576 +892,610 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G1048576"/>
   <sheetFormatPr defaultColWidth="11.1484375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="60.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="164"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="60.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="164"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" s="4" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" s="4" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G10" s="0" t="s">
+      <c r="G10" s="4" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="0" t="s">
+      <c r="G11" s="4" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G12" s="0" t="s">
+      <c r="G12" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="0" t="s">
+      <c r="G13" s="4" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="G14" s="0" t="s">
+      <c r="G14" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="0" t="s">
+      <c r="G15" s="4" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="G16" s="0" t="s">
+      <c r="G16" s="4" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="G17" s="0" t="s">
+      <c r="G17" s="4" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G18" s="0" t="s">
+      <c r="G18" s="4" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G19" s="0" t="s">
+      <c r="G19" s="4" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G20" s="0" t="s">
+      <c r="G20" s="4" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="G21" s="0" t="s">
+      <c r="G21" s="4" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="E22" s="0" t="s">
+      <c r="E22" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="G22" s="0" t="s">
+      <c r="G22" s="4" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E23" s="0" t="s">
+      <c r="E23" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G23" s="0" t="s">
+      <c r="G23" s="4" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="E24" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="G24" s="0" t="s">
+      <c r="G24" s="4" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="7"/>
-      <c r="E27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="8"/>
-    </row>
+    <row r="1048536" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048537" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048538" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048539" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048540" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048541" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048542" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048543" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048544" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048545" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048548" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048549" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048550" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048551" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" display="10.1016/j.brainres.2018.03.012; 10.3171/jns.2005.103.1.0136; 10.1161/01.STR.0000170712.46106.2e"/>
@@ -1497,9 +1519,9 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultColWidth="11.1484375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="27.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="52.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1517,80 +1539,80 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="4" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="4" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="4" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="4" t="s">
         <v>148</v>
       </c>
       <c r="C7" s="10" t="s">

--- a/data/__gene_data.xlsx
+++ b/data/__gene_data.xlsx
@@ -233,7 +233,7 @@
     <t xml:space="preserve">NM_011593.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Lect1 </t>
+    <t xml:space="preserve">Lect1</t>
   </si>
   <si>
     <t xml:space="preserve">chondromodulin</t>
@@ -1413,7 +1413,7 @@
       <c r="A23" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="5" t="s">
@@ -1436,7 +1436,7 @@
       <c r="A24" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="5" t="s">
